--- a/coaching_forms/047_sports_training_contact_form--coaching_forms.xlsx
+++ b/coaching_forms/047_sports_training_contact_form--coaching_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Email Error</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Availability Error</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Preferred Time Error</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Training Experience Error</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Goal Error</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Sport Error</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Contact Method Error</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Comment Error</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Error Message</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>sport</t>
+          <t>sport_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>sport</t>
+          <t>Sport 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>contact_method_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>Contact Method 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>comment_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>comment</t>
+          <t>Comment 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>first_name_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>First Name 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>availability</t>
+          <t>availability_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>availability</t>
+          <t>Availability 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sport_choices</t>
+          <t>sport_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>sport_choices</t>
+          <t>sport_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>sport_choices</t>
+          <t>sport_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sport_choices</t>
+          <t>sport_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1619,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sport_choices</t>
+          <t>sport_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>availability_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>availability_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>availability_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>availability_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1772,7 +1772,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>availability_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1789,7 +1789,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>availability_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1806,7 +1806,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>availability_choices</t>
+          <t>availability_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
